--- a/Tests/Resources/StemDictionaries.xlsx
+++ b/Tests/Resources/StemDictionaries.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucav\Nextcloud\STEM-ELECTRONICS\StemDeviceManager\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucav\source\repos\bitbucket\StemDeviceManager\GUI.Windows\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0060BD44-28F8-4742-B87F-EBEA0B099D52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08B259F7-01CF-4E8A-8947-2470824AFB2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" tabRatio="500" firstSheet="18" activeTab="20" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="500" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="COMANDI" sheetId="1" r:id="rId1"/>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3974" uniqueCount="1032">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3980" uniqueCount="1037">
   <si>
     <t>NOME COMANDO</t>
   </si>
@@ -4197,6 +4197,21 @@
   </si>
   <si>
     <t>Computer</t>
+  </si>
+  <si>
+    <t>0x00000101</t>
+  </si>
+  <si>
+    <t>0x0000013F</t>
+  </si>
+  <si>
+    <t>0x000C0101</t>
+  </si>
+  <si>
+    <t>0x000C0102</t>
+  </si>
+  <si>
+    <t>0x000C0103</t>
   </si>
 </sst>
 </file>
@@ -4883,24 +4898,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4915,6 +4912,24 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5354,13 +5369,13 @@
       <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="99" t="s">
+      <c r="D1" s="105" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="99"/>
-      <c r="F1" s="99"/>
-      <c r="G1" s="99"/>
-      <c r="H1" s="99"/>
+      <c r="E1" s="105"/>
+      <c r="F1" s="105"/>
+      <c r="G1" s="105"/>
+      <c r="H1" s="105"/>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A2" s="89" t="s">
@@ -6999,18 +7014,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="103" t="s">
+      <c r="A1" s="104" t="s">
         <v>765</v>
       </c>
-      <c r="B1" s="103"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="103"/>
-      <c r="E1" s="103"/>
-      <c r="F1" s="103"/>
-      <c r="G1" s="103"/>
-      <c r="H1" s="103"/>
-      <c r="I1" s="103"/>
-      <c r="J1" s="103"/>
+      <c r="B1" s="104"/>
+      <c r="C1" s="104"/>
+      <c r="D1" s="104"/>
+      <c r="E1" s="104"/>
+      <c r="F1" s="104"/>
+      <c r="G1" s="104"/>
+      <c r="H1" s="104"/>
+      <c r="I1" s="104"/>
+      <c r="J1" s="104"/>
       <c r="K1" s="3"/>
     </row>
     <row r="2" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -7023,10 +7038,10 @@
       <c r="A3" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="B3" s="105" t="s">
+      <c r="B3" s="99" t="s">
         <v>486</v>
       </c>
-      <c r="C3" s="106"/>
+      <c r="C3" s="100"/>
       <c r="D3" s="2" t="s">
         <v>82</v>
       </c>
@@ -7074,16 +7089,16 @@
       <c r="H4" s="111"/>
       <c r="I4" s="111"/>
       <c r="J4" s="113"/>
-      <c r="K4" s="107"/>
-      <c r="L4" s="108"/>
-      <c r="M4" s="108"/>
-      <c r="N4" s="108"/>
-      <c r="O4" s="108"/>
-      <c r="P4" s="108"/>
-      <c r="Q4" s="108"/>
-      <c r="R4" s="108"/>
-      <c r="S4" s="108"/>
-      <c r="T4" s="109"/>
+      <c r="K4" s="101"/>
+      <c r="L4" s="102"/>
+      <c r="M4" s="102"/>
+      <c r="N4" s="102"/>
+      <c r="O4" s="102"/>
+      <c r="P4" s="102"/>
+      <c r="Q4" s="102"/>
+      <c r="R4" s="102"/>
+      <c r="S4" s="102"/>
+      <c r="T4" s="103"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="46" t="str">
@@ -8340,28 +8355,28 @@
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A38" s="107" t="s">
+      <c r="A38" s="101" t="s">
         <v>487</v>
       </c>
-      <c r="B38" s="108"/>
-      <c r="C38" s="108"/>
-      <c r="D38" s="108"/>
-      <c r="E38" s="108"/>
-      <c r="F38" s="108"/>
-      <c r="G38" s="108"/>
-      <c r="H38" s="108"/>
-      <c r="I38" s="108"/>
-      <c r="J38" s="109"/>
-      <c r="K38" s="107"/>
-      <c r="L38" s="108"/>
-      <c r="M38" s="108"/>
-      <c r="N38" s="108"/>
-      <c r="O38" s="108"/>
-      <c r="P38" s="108"/>
-      <c r="Q38" s="108"/>
-      <c r="R38" s="108"/>
-      <c r="S38" s="108"/>
-      <c r="T38" s="109"/>
+      <c r="B38" s="102"/>
+      <c r="C38" s="102"/>
+      <c r="D38" s="102"/>
+      <c r="E38" s="102"/>
+      <c r="F38" s="102"/>
+      <c r="G38" s="102"/>
+      <c r="H38" s="102"/>
+      <c r="I38" s="102"/>
+      <c r="J38" s="103"/>
+      <c r="K38" s="101"/>
+      <c r="L38" s="102"/>
+      <c r="M38" s="102"/>
+      <c r="N38" s="102"/>
+      <c r="O38" s="102"/>
+      <c r="P38" s="102"/>
+      <c r="Q38" s="102"/>
+      <c r="R38" s="102"/>
+      <c r="S38" s="102"/>
+      <c r="T38" s="103"/>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39" s="15" t="s">
@@ -8666,15 +8681,15 @@
       </c>
       <c r="K47" s="3"/>
       <c r="L47" s="1"/>
-      <c r="M47" s="104" t="s">
+      <c r="M47" s="109" t="s">
         <v>154</v>
       </c>
-      <c r="N47" s="104"/>
-      <c r="O47" s="104"/>
-      <c r="P47" s="104"/>
-      <c r="Q47" s="104"/>
-      <c r="R47" s="104"/>
-      <c r="S47" s="104"/>
+      <c r="N47" s="109"/>
+      <c r="O47" s="109"/>
+      <c r="P47" s="109"/>
+      <c r="Q47" s="109"/>
+      <c r="R47" s="109"/>
+      <c r="S47" s="109"/>
       <c r="T47" s="1"/>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.25">
@@ -8703,13 +8718,13 @@
       <c r="L48" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="M48" s="104"/>
-      <c r="N48" s="104"/>
-      <c r="O48" s="104"/>
-      <c r="P48" s="104"/>
-      <c r="Q48" s="104"/>
-      <c r="R48" s="104"/>
-      <c r="S48" s="104"/>
+      <c r="M48" s="109"/>
+      <c r="N48" s="109"/>
+      <c r="O48" s="109"/>
+      <c r="P48" s="109"/>
+      <c r="Q48" s="109"/>
+      <c r="R48" s="109"/>
+      <c r="S48" s="109"/>
       <c r="T48" s="1"/>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.25">
@@ -8738,13 +8753,13 @@
       </c>
       <c r="K49" s="3"/>
       <c r="L49" s="1"/>
-      <c r="M49" s="104"/>
-      <c r="N49" s="104"/>
-      <c r="O49" s="104"/>
-      <c r="P49" s="104"/>
-      <c r="Q49" s="104"/>
-      <c r="R49" s="104"/>
-      <c r="S49" s="104"/>
+      <c r="M49" s="109"/>
+      <c r="N49" s="109"/>
+      <c r="O49" s="109"/>
+      <c r="P49" s="109"/>
+      <c r="Q49" s="109"/>
+      <c r="R49" s="109"/>
+      <c r="S49" s="109"/>
       <c r="T49" s="1"/>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.25">
@@ -8775,13 +8790,13 @@
       <c r="L50" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="M50" s="104"/>
-      <c r="N50" s="104"/>
-      <c r="O50" s="104"/>
-      <c r="P50" s="104"/>
-      <c r="Q50" s="104"/>
-      <c r="R50" s="104"/>
-      <c r="S50" s="104"/>
+      <c r="M50" s="109"/>
+      <c r="N50" s="109"/>
+      <c r="O50" s="109"/>
+      <c r="P50" s="109"/>
+      <c r="Q50" s="109"/>
+      <c r="R50" s="109"/>
+      <c r="S50" s="109"/>
       <c r="T50" s="1"/>
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.25">
@@ -8812,13 +8827,13 @@
       <c r="L51" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="M51" s="104"/>
-      <c r="N51" s="104"/>
-      <c r="O51" s="104"/>
-      <c r="P51" s="104"/>
-      <c r="Q51" s="104"/>
-      <c r="R51" s="104"/>
-      <c r="S51" s="104"/>
+      <c r="M51" s="109"/>
+      <c r="N51" s="109"/>
+      <c r="O51" s="109"/>
+      <c r="P51" s="109"/>
+      <c r="Q51" s="109"/>
+      <c r="R51" s="109"/>
+      <c r="S51" s="109"/>
       <c r="T51" s="1"/>
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.25">
@@ -8846,13 +8861,13 @@
       </c>
       <c r="K52" s="3"/>
       <c r="L52" s="1"/>
-      <c r="M52" s="104"/>
-      <c r="N52" s="104"/>
-      <c r="O52" s="104"/>
-      <c r="P52" s="104"/>
-      <c r="Q52" s="104"/>
-      <c r="R52" s="104"/>
-      <c r="S52" s="104"/>
+      <c r="M52" s="109"/>
+      <c r="N52" s="109"/>
+      <c r="O52" s="109"/>
+      <c r="P52" s="109"/>
+      <c r="Q52" s="109"/>
+      <c r="R52" s="109"/>
+      <c r="S52" s="109"/>
       <c r="T52" s="1"/>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.25">
@@ -8879,13 +8894,13 @@
       <c r="L53" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="M53" s="104"/>
-      <c r="N53" s="104"/>
-      <c r="O53" s="104"/>
-      <c r="P53" s="104"/>
-      <c r="Q53" s="104"/>
-      <c r="R53" s="104"/>
-      <c r="S53" s="104"/>
+      <c r="M53" s="109"/>
+      <c r="N53" s="109"/>
+      <c r="O53" s="109"/>
+      <c r="P53" s="109"/>
+      <c r="Q53" s="109"/>
+      <c r="R53" s="109"/>
+      <c r="S53" s="109"/>
       <c r="T53" s="1"/>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.25">
@@ -8910,13 +8925,13 @@
       </c>
       <c r="K54" s="3"/>
       <c r="L54" s="1"/>
-      <c r="M54" s="104"/>
-      <c r="N54" s="104"/>
-      <c r="O54" s="104"/>
-      <c r="P54" s="104"/>
-      <c r="Q54" s="104"/>
-      <c r="R54" s="104"/>
-      <c r="S54" s="104"/>
+      <c r="M54" s="109"/>
+      <c r="N54" s="109"/>
+      <c r="O54" s="109"/>
+      <c r="P54" s="109"/>
+      <c r="Q54" s="109"/>
+      <c r="R54" s="109"/>
+      <c r="S54" s="109"/>
       <c r="T54" s="1"/>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.25">
@@ -8943,13 +8958,13 @@
       <c r="L55" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="M55" s="104"/>
-      <c r="N55" s="104"/>
-      <c r="O55" s="104"/>
-      <c r="P55" s="104"/>
-      <c r="Q55" s="104"/>
-      <c r="R55" s="104"/>
-      <c r="S55" s="104"/>
+      <c r="M55" s="109"/>
+      <c r="N55" s="109"/>
+      <c r="O55" s="109"/>
+      <c r="P55" s="109"/>
+      <c r="Q55" s="109"/>
+      <c r="R55" s="109"/>
+      <c r="S55" s="109"/>
       <c r="T55" s="1"/>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.25">
@@ -8977,13 +8992,13 @@
       <c r="L56" s="17" t="s">
         <v>156</v>
       </c>
-      <c r="M56" s="104"/>
-      <c r="N56" s="104"/>
-      <c r="O56" s="104"/>
-      <c r="P56" s="104"/>
-      <c r="Q56" s="104"/>
-      <c r="R56" s="104"/>
-      <c r="S56" s="104"/>
+      <c r="M56" s="109"/>
+      <c r="N56" s="109"/>
+      <c r="O56" s="109"/>
+      <c r="P56" s="109"/>
+      <c r="Q56" s="109"/>
+      <c r="R56" s="109"/>
+      <c r="S56" s="109"/>
       <c r="T56" s="1"/>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.25">
@@ -9009,13 +9024,13 @@
       </c>
       <c r="K57" s="3"/>
       <c r="L57" s="1"/>
-      <c r="M57" s="104"/>
-      <c r="N57" s="104"/>
-      <c r="O57" s="104"/>
-      <c r="P57" s="104"/>
-      <c r="Q57" s="104"/>
-      <c r="R57" s="104"/>
-      <c r="S57" s="104"/>
+      <c r="M57" s="109"/>
+      <c r="N57" s="109"/>
+      <c r="O57" s="109"/>
+      <c r="P57" s="109"/>
+      <c r="Q57" s="109"/>
+      <c r="R57" s="109"/>
+      <c r="S57" s="109"/>
       <c r="T57" s="1"/>
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.25">
@@ -9452,16 +9467,16 @@
       <c r="I77" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="K77" s="100"/>
-      <c r="L77" s="100"/>
-      <c r="M77" s="100"/>
-      <c r="N77" s="100"/>
-      <c r="O77" s="100"/>
-      <c r="P77" s="100"/>
-      <c r="Q77" s="100"/>
-      <c r="R77" s="100"/>
-      <c r="S77" s="100"/>
-      <c r="T77" s="100"/>
+      <c r="K77" s="106"/>
+      <c r="L77" s="106"/>
+      <c r="M77" s="106"/>
+      <c r="N77" s="106"/>
+      <c r="O77" s="106"/>
+      <c r="P77" s="106"/>
+      <c r="Q77" s="106"/>
+      <c r="R77" s="106"/>
+      <c r="S77" s="106"/>
+      <c r="T77" s="106"/>
     </row>
     <row r="78" spans="1:20" ht="60" x14ac:dyDescent="0.25">
       <c r="A78" s="21" t="s">
@@ -9745,18 +9760,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A1" s="103" t="s">
+      <c r="A1" s="104" t="s">
         <v>765</v>
       </c>
-      <c r="B1" s="103"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="103"/>
-      <c r="E1" s="103"/>
-      <c r="F1" s="103"/>
-      <c r="G1" s="103"/>
-      <c r="H1" s="103"/>
-      <c r="I1" s="103"/>
-      <c r="J1" s="103"/>
+      <c r="B1" s="104"/>
+      <c r="C1" s="104"/>
+      <c r="D1" s="104"/>
+      <c r="E1" s="104"/>
+      <c r="F1" s="104"/>
+      <c r="G1" s="104"/>
+      <c r="H1" s="104"/>
+      <c r="I1" s="104"/>
+      <c r="J1" s="104"/>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -9826,16 +9841,16 @@
       <c r="H4" s="53"/>
       <c r="I4" s="53"/>
       <c r="J4" s="74"/>
-      <c r="K4" s="107"/>
-      <c r="L4" s="108"/>
-      <c r="M4" s="108"/>
-      <c r="N4" s="108"/>
-      <c r="O4" s="108"/>
-      <c r="P4" s="108"/>
-      <c r="Q4" s="108"/>
-      <c r="R4" s="108"/>
-      <c r="S4" s="108"/>
-      <c r="T4" s="109"/>
+      <c r="K4" s="101"/>
+      <c r="L4" s="102"/>
+      <c r="M4" s="102"/>
+      <c r="N4" s="102"/>
+      <c r="O4" s="102"/>
+      <c r="P4" s="102"/>
+      <c r="Q4" s="102"/>
+      <c r="R4" s="102"/>
+      <c r="S4" s="102"/>
+      <c r="T4" s="103"/>
       <c r="U4" s="80"/>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.25">
@@ -11278,13 +11293,13 @@
       </c>
       <c r="J36" s="3"/>
       <c r="K36" s="22"/>
-      <c r="L36" s="104"/>
-      <c r="M36" s="104"/>
-      <c r="N36" s="104"/>
-      <c r="O36" s="104"/>
-      <c r="P36" s="104"/>
-      <c r="Q36" s="104"/>
-      <c r="R36" s="104"/>
+      <c r="L36" s="109"/>
+      <c r="M36" s="109"/>
+      <c r="N36" s="109"/>
+      <c r="O36" s="109"/>
+      <c r="P36" s="109"/>
+      <c r="Q36" s="109"/>
+      <c r="R36" s="109"/>
       <c r="S36" s="1"/>
       <c r="U36" s="80"/>
     </row>
@@ -11312,13 +11327,13 @@
       </c>
       <c r="J37" s="3"/>
       <c r="K37" s="22"/>
-      <c r="L37" s="104"/>
-      <c r="M37" s="104"/>
-      <c r="N37" s="104"/>
-      <c r="O37" s="104"/>
-      <c r="P37" s="104"/>
-      <c r="Q37" s="104"/>
-      <c r="R37" s="104"/>
+      <c r="L37" s="109"/>
+      <c r="M37" s="109"/>
+      <c r="N37" s="109"/>
+      <c r="O37" s="109"/>
+      <c r="P37" s="109"/>
+      <c r="Q37" s="109"/>
+      <c r="R37" s="109"/>
       <c r="S37" s="1"/>
       <c r="U37" s="80"/>
     </row>
@@ -11345,13 +11360,13 @@
       </c>
       <c r="J38" s="3"/>
       <c r="K38" s="22"/>
-      <c r="L38" s="104"/>
-      <c r="M38" s="104"/>
-      <c r="N38" s="104"/>
-      <c r="O38" s="104"/>
-      <c r="P38" s="104"/>
-      <c r="Q38" s="104"/>
-      <c r="R38" s="104"/>
+      <c r="L38" s="109"/>
+      <c r="M38" s="109"/>
+      <c r="N38" s="109"/>
+      <c r="O38" s="109"/>
+      <c r="P38" s="109"/>
+      <c r="Q38" s="109"/>
+      <c r="R38" s="109"/>
       <c r="S38" s="1"/>
       <c r="U38" s="80"/>
     </row>
@@ -11378,13 +11393,13 @@
       </c>
       <c r="J39" s="3"/>
       <c r="K39" s="22"/>
-      <c r="L39" s="104"/>
-      <c r="M39" s="104"/>
-      <c r="N39" s="104"/>
-      <c r="O39" s="104"/>
-      <c r="P39" s="104"/>
-      <c r="Q39" s="104"/>
-      <c r="R39" s="104"/>
+      <c r="L39" s="109"/>
+      <c r="M39" s="109"/>
+      <c r="N39" s="109"/>
+      <c r="O39" s="109"/>
+      <c r="P39" s="109"/>
+      <c r="Q39" s="109"/>
+      <c r="R39" s="109"/>
       <c r="S39" s="1"/>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
@@ -11410,13 +11425,13 @@
       </c>
       <c r="J40" s="3"/>
       <c r="K40" s="22"/>
-      <c r="L40" s="104"/>
-      <c r="M40" s="104"/>
-      <c r="N40" s="104"/>
-      <c r="O40" s="104"/>
-      <c r="P40" s="104"/>
-      <c r="Q40" s="104"/>
-      <c r="R40" s="104"/>
+      <c r="L40" s="109"/>
+      <c r="M40" s="109"/>
+      <c r="N40" s="109"/>
+      <c r="O40" s="109"/>
+      <c r="P40" s="109"/>
+      <c r="Q40" s="109"/>
+      <c r="R40" s="109"/>
       <c r="S40" s="1"/>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
@@ -11441,13 +11456,13 @@
       </c>
       <c r="J41" s="3"/>
       <c r="K41" s="22"/>
-      <c r="L41" s="104"/>
-      <c r="M41" s="104"/>
-      <c r="N41" s="104"/>
-      <c r="O41" s="104"/>
-      <c r="P41" s="104"/>
-      <c r="Q41" s="104"/>
-      <c r="R41" s="104"/>
+      <c r="L41" s="109"/>
+      <c r="M41" s="109"/>
+      <c r="N41" s="109"/>
+      <c r="O41" s="109"/>
+      <c r="P41" s="109"/>
+      <c r="Q41" s="109"/>
+      <c r="R41" s="109"/>
       <c r="S41" s="1"/>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
@@ -11472,13 +11487,13 @@
       </c>
       <c r="J42" s="3"/>
       <c r="K42" s="22"/>
-      <c r="L42" s="104"/>
-      <c r="M42" s="104"/>
-      <c r="N42" s="104"/>
-      <c r="O42" s="104"/>
-      <c r="P42" s="104"/>
-      <c r="Q42" s="104"/>
-      <c r="R42" s="104"/>
+      <c r="L42" s="109"/>
+      <c r="M42" s="109"/>
+      <c r="N42" s="109"/>
+      <c r="O42" s="109"/>
+      <c r="P42" s="109"/>
+      <c r="Q42" s="109"/>
+      <c r="R42" s="109"/>
       <c r="S42" s="1"/>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
@@ -11503,13 +11518,13 @@
       </c>
       <c r="J43" s="3"/>
       <c r="K43" s="22"/>
-      <c r="L43" s="104"/>
-      <c r="M43" s="104"/>
-      <c r="N43" s="104"/>
-      <c r="O43" s="104"/>
-      <c r="P43" s="104"/>
-      <c r="Q43" s="104"/>
-      <c r="R43" s="104"/>
+      <c r="L43" s="109"/>
+      <c r="M43" s="109"/>
+      <c r="N43" s="109"/>
+      <c r="O43" s="109"/>
+      <c r="P43" s="109"/>
+      <c r="Q43" s="109"/>
+      <c r="R43" s="109"/>
       <c r="S43" s="1"/>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
@@ -11534,13 +11549,13 @@
       </c>
       <c r="J44" s="3"/>
       <c r="K44" s="22"/>
-      <c r="L44" s="104"/>
-      <c r="M44" s="104"/>
-      <c r="N44" s="104"/>
-      <c r="O44" s="104"/>
-      <c r="P44" s="104"/>
-      <c r="Q44" s="104"/>
-      <c r="R44" s="104"/>
+      <c r="L44" s="109"/>
+      <c r="M44" s="109"/>
+      <c r="N44" s="109"/>
+      <c r="O44" s="109"/>
+      <c r="P44" s="109"/>
+      <c r="Q44" s="109"/>
+      <c r="R44" s="109"/>
       <c r="S44" s="1"/>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
@@ -11566,13 +11581,13 @@
       </c>
       <c r="J45" s="3"/>
       <c r="K45" s="22"/>
-      <c r="L45" s="104"/>
-      <c r="M45" s="104"/>
-      <c r="N45" s="104"/>
-      <c r="O45" s="104"/>
-      <c r="P45" s="104"/>
-      <c r="Q45" s="104"/>
-      <c r="R45" s="104"/>
+      <c r="L45" s="109"/>
+      <c r="M45" s="109"/>
+      <c r="N45" s="109"/>
+      <c r="O45" s="109"/>
+      <c r="P45" s="109"/>
+      <c r="Q45" s="109"/>
+      <c r="R45" s="109"/>
       <c r="S45" s="1"/>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
@@ -11598,13 +11613,13 @@
       </c>
       <c r="J46" s="3"/>
       <c r="K46" s="22"/>
-      <c r="L46" s="104"/>
-      <c r="M46" s="104"/>
-      <c r="N46" s="104"/>
-      <c r="O46" s="104"/>
-      <c r="P46" s="104"/>
-      <c r="Q46" s="104"/>
-      <c r="R46" s="104"/>
+      <c r="L46" s="109"/>
+      <c r="M46" s="109"/>
+      <c r="N46" s="109"/>
+      <c r="O46" s="109"/>
+      <c r="P46" s="109"/>
+      <c r="Q46" s="109"/>
+      <c r="R46" s="109"/>
       <c r="S46" s="1"/>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
@@ -11772,25 +11787,25 @@
       <c r="T51" s="80"/>
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A52" s="107"/>
-      <c r="B52" s="108"/>
-      <c r="C52" s="108"/>
-      <c r="D52" s="108"/>
-      <c r="E52" s="108"/>
-      <c r="F52" s="108"/>
-      <c r="G52" s="108"/>
-      <c r="H52" s="108"/>
-      <c r="I52" s="109"/>
-      <c r="J52" s="100"/>
-      <c r="K52" s="100"/>
-      <c r="L52" s="100"/>
-      <c r="M52" s="100"/>
-      <c r="N52" s="100"/>
-      <c r="O52" s="100"/>
-      <c r="P52" s="100"/>
-      <c r="Q52" s="100"/>
-      <c r="R52" s="100"/>
-      <c r="S52" s="100"/>
+      <c r="A52" s="101"/>
+      <c r="B52" s="102"/>
+      <c r="C52" s="102"/>
+      <c r="D52" s="102"/>
+      <c r="E52" s="102"/>
+      <c r="F52" s="102"/>
+      <c r="G52" s="102"/>
+      <c r="H52" s="102"/>
+      <c r="I52" s="103"/>
+      <c r="J52" s="106"/>
+      <c r="K52" s="106"/>
+      <c r="L52" s="106"/>
+      <c r="M52" s="106"/>
+      <c r="N52" s="106"/>
+      <c r="O52" s="106"/>
+      <c r="P52" s="106"/>
+      <c r="Q52" s="106"/>
+      <c r="R52" s="106"/>
+      <c r="S52" s="106"/>
       <c r="T52" s="80"/>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.25">
@@ -12371,18 +12386,18 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="100" t="s">
+      <c r="A2" s="106" t="s">
         <v>229</v>
       </c>
-      <c r="B2" s="100"/>
-      <c r="C2" s="100"/>
-      <c r="D2" s="100"/>
-      <c r="E2" s="100"/>
-      <c r="F2" s="100"/>
-      <c r="G2" s="100"/>
-      <c r="H2" s="100"/>
-      <c r="I2" s="100"/>
-      <c r="J2" s="100"/>
+      <c r="B2" s="106"/>
+      <c r="C2" s="106"/>
+      <c r="D2" s="106"/>
+      <c r="E2" s="106"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="106"/>
+      <c r="H2" s="106"/>
+      <c r="I2" s="106"/>
+      <c r="J2" s="106"/>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
@@ -13069,18 +13084,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1" s="103" t="s">
+      <c r="A1" s="104" t="s">
         <v>765</v>
       </c>
-      <c r="B1" s="103"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="103"/>
-      <c r="E1" s="103"/>
-      <c r="F1" s="103"/>
-      <c r="G1" s="103"/>
-      <c r="H1" s="103"/>
-      <c r="I1" s="103"/>
-      <c r="J1" s="103"/>
+      <c r="B1" s="104"/>
+      <c r="C1" s="104"/>
+      <c r="D1" s="104"/>
+      <c r="E1" s="104"/>
+      <c r="F1" s="104"/>
+      <c r="G1" s="104"/>
+      <c r="H1" s="104"/>
+      <c r="I1" s="104"/>
+      <c r="J1" s="104"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -13093,10 +13108,10 @@
       <c r="A3" s="10" t="s">
         <v>764</v>
       </c>
-      <c r="B3" s="105" t="s">
+      <c r="B3" s="99" t="s">
         <v>486</v>
       </c>
-      <c r="C3" s="106"/>
+      <c r="C3" s="100"/>
       <c r="D3" s="2" t="s">
         <v>82</v>
       </c>
@@ -13152,16 +13167,16 @@
       <c r="H4" s="53"/>
       <c r="I4" s="53"/>
       <c r="J4" s="74"/>
-      <c r="K4" s="107"/>
-      <c r="L4" s="108"/>
-      <c r="M4" s="108"/>
-      <c r="N4" s="108"/>
-      <c r="O4" s="108"/>
-      <c r="P4" s="108"/>
-      <c r="Q4" s="108"/>
-      <c r="R4" s="108"/>
-      <c r="S4" s="108"/>
-      <c r="T4" s="109"/>
+      <c r="K4" s="101"/>
+      <c r="L4" s="102"/>
+      <c r="M4" s="102"/>
+      <c r="N4" s="102"/>
+      <c r="O4" s="102"/>
+      <c r="P4" s="102"/>
+      <c r="Q4" s="102"/>
+      <c r="R4" s="102"/>
+      <c r="S4" s="102"/>
+      <c r="T4" s="103"/>
     </row>
     <row r="5" spans="1:20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="37" t="str">
@@ -14341,16 +14356,16 @@
       <c r="H29" s="53"/>
       <c r="I29" s="53"/>
       <c r="J29" s="53"/>
-      <c r="K29" s="107"/>
-      <c r="L29" s="108"/>
-      <c r="M29" s="108"/>
-      <c r="N29" s="108"/>
-      <c r="O29" s="108"/>
-      <c r="P29" s="108"/>
-      <c r="Q29" s="108"/>
-      <c r="R29" s="108"/>
-      <c r="S29" s="108"/>
-      <c r="T29" s="109"/>
+      <c r="K29" s="101"/>
+      <c r="L29" s="102"/>
+      <c r="M29" s="102"/>
+      <c r="N29" s="102"/>
+      <c r="O29" s="102"/>
+      <c r="P29" s="102"/>
+      <c r="Q29" s="102"/>
+      <c r="R29" s="102"/>
+      <c r="S29" s="102"/>
+      <c r="T29" s="103"/>
     </row>
     <row r="30" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
@@ -18435,18 +18450,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1" s="103" t="s">
+      <c r="A1" s="104" t="s">
         <v>765</v>
       </c>
-      <c r="B1" s="103"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="103"/>
-      <c r="E1" s="103"/>
-      <c r="F1" s="103"/>
-      <c r="G1" s="103"/>
-      <c r="H1" s="103"/>
-      <c r="I1" s="103"/>
-      <c r="J1" s="103"/>
+      <c r="B1" s="104"/>
+      <c r="C1" s="104"/>
+      <c r="D1" s="104"/>
+      <c r="E1" s="104"/>
+      <c r="F1" s="104"/>
+      <c r="G1" s="104"/>
+      <c r="H1" s="104"/>
+      <c r="I1" s="104"/>
+      <c r="J1" s="104"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -18459,10 +18474,10 @@
       <c r="A3" s="10" t="s">
         <v>790</v>
       </c>
-      <c r="B3" s="105" t="s">
+      <c r="B3" s="99" t="s">
         <v>486</v>
       </c>
-      <c r="C3" s="106"/>
+      <c r="C3" s="100"/>
       <c r="D3" s="2" t="s">
         <v>82</v>
       </c>
@@ -18518,16 +18533,16 @@
       <c r="H4" s="53"/>
       <c r="I4" s="53"/>
       <c r="J4" s="74"/>
-      <c r="K4" s="107"/>
-      <c r="L4" s="108"/>
-      <c r="M4" s="108"/>
-      <c r="N4" s="108"/>
-      <c r="O4" s="108"/>
-      <c r="P4" s="108"/>
-      <c r="Q4" s="108"/>
-      <c r="R4" s="108"/>
-      <c r="S4" s="108"/>
-      <c r="T4" s="109"/>
+      <c r="K4" s="101"/>
+      <c r="L4" s="102"/>
+      <c r="M4" s="102"/>
+      <c r="N4" s="102"/>
+      <c r="O4" s="102"/>
+      <c r="P4" s="102"/>
+      <c r="Q4" s="102"/>
+      <c r="R4" s="102"/>
+      <c r="S4" s="102"/>
+      <c r="T4" s="103"/>
     </row>
     <row r="5" spans="1:20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="37" t="str">
@@ -19695,16 +19710,16 @@
       <c r="H29" s="53"/>
       <c r="I29" s="53"/>
       <c r="J29" s="53"/>
-      <c r="K29" s="107"/>
-      <c r="L29" s="108"/>
-      <c r="M29" s="108"/>
-      <c r="N29" s="108"/>
-      <c r="O29" s="108"/>
-      <c r="P29" s="108"/>
-      <c r="Q29" s="108"/>
-      <c r="R29" s="108"/>
-      <c r="S29" s="108"/>
-      <c r="T29" s="109"/>
+      <c r="K29" s="101"/>
+      <c r="L29" s="102"/>
+      <c r="M29" s="102"/>
+      <c r="N29" s="102"/>
+      <c r="O29" s="102"/>
+      <c r="P29" s="102"/>
+      <c r="Q29" s="102"/>
+      <c r="R29" s="102"/>
+      <c r="S29" s="102"/>
+      <c r="T29" s="103"/>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
@@ -22932,18 +22947,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1" s="103" t="s">
+      <c r="A1" s="104" t="s">
         <v>765</v>
       </c>
-      <c r="B1" s="103"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="103"/>
-      <c r="E1" s="103"/>
-      <c r="F1" s="103"/>
-      <c r="G1" s="103"/>
-      <c r="H1" s="103"/>
-      <c r="I1" s="103"/>
-      <c r="J1" s="103"/>
+      <c r="B1" s="104"/>
+      <c r="C1" s="104"/>
+      <c r="D1" s="104"/>
+      <c r="E1" s="104"/>
+      <c r="F1" s="104"/>
+      <c r="G1" s="104"/>
+      <c r="H1" s="104"/>
+      <c r="I1" s="104"/>
+      <c r="J1" s="104"/>
       <c r="K1" s="3"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
@@ -23010,16 +23025,16 @@
       <c r="H4" s="55"/>
       <c r="I4" s="55"/>
       <c r="J4" s="56"/>
-      <c r="K4" s="107"/>
-      <c r="L4" s="108"/>
-      <c r="M4" s="108"/>
-      <c r="N4" s="108"/>
-      <c r="O4" s="108"/>
-      <c r="P4" s="108"/>
-      <c r="Q4" s="108"/>
-      <c r="R4" s="108"/>
-      <c r="S4" s="108"/>
-      <c r="T4" s="109"/>
+      <c r="K4" s="101"/>
+      <c r="L4" s="102"/>
+      <c r="M4" s="102"/>
+      <c r="N4" s="102"/>
+      <c r="O4" s="102"/>
+      <c r="P4" s="102"/>
+      <c r="Q4" s="102"/>
+      <c r="R4" s="102"/>
+      <c r="S4" s="102"/>
+      <c r="T4" s="103"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="37" t="str">
@@ -24853,18 +24868,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1" s="103" t="s">
+      <c r="A1" s="104" t="s">
         <v>765</v>
       </c>
-      <c r="B1" s="103"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="103"/>
-      <c r="E1" s="103"/>
-      <c r="F1" s="103"/>
-      <c r="G1" s="103"/>
-      <c r="H1" s="103"/>
-      <c r="I1" s="103"/>
-      <c r="J1" s="103"/>
+      <c r="B1" s="104"/>
+      <c r="C1" s="104"/>
+      <c r="D1" s="104"/>
+      <c r="E1" s="104"/>
+      <c r="F1" s="104"/>
+      <c r="G1" s="104"/>
+      <c r="H1" s="104"/>
+      <c r="I1" s="104"/>
+      <c r="J1" s="104"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -24877,10 +24892,10 @@
       <c r="A3" s="10" t="s">
         <v>884</v>
       </c>
-      <c r="B3" s="105" t="s">
+      <c r="B3" s="99" t="s">
         <v>486</v>
       </c>
-      <c r="C3" s="106"/>
+      <c r="C3" s="100"/>
       <c r="D3" s="2" t="s">
         <v>82</v>
       </c>
@@ -24936,16 +24951,16 @@
       <c r="H4" s="53"/>
       <c r="I4" s="53"/>
       <c r="J4" s="74"/>
-      <c r="K4" s="107"/>
-      <c r="L4" s="108"/>
-      <c r="M4" s="108"/>
-      <c r="N4" s="108"/>
-      <c r="O4" s="108"/>
-      <c r="P4" s="108"/>
-      <c r="Q4" s="108"/>
-      <c r="R4" s="108"/>
-      <c r="S4" s="108"/>
-      <c r="T4" s="109"/>
+      <c r="K4" s="101"/>
+      <c r="L4" s="102"/>
+      <c r="M4" s="102"/>
+      <c r="N4" s="102"/>
+      <c r="O4" s="102"/>
+      <c r="P4" s="102"/>
+      <c r="Q4" s="102"/>
+      <c r="R4" s="102"/>
+      <c r="S4" s="102"/>
+      <c r="T4" s="103"/>
     </row>
     <row r="5" spans="1:20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="37" t="str">
@@ -26158,16 +26173,16 @@
       <c r="H29" s="53"/>
       <c r="I29" s="53"/>
       <c r="J29" s="53"/>
-      <c r="K29" s="107"/>
-      <c r="L29" s="108"/>
-      <c r="M29" s="108"/>
-      <c r="N29" s="108"/>
-      <c r="O29" s="108"/>
-      <c r="P29" s="108"/>
-      <c r="Q29" s="108"/>
-      <c r="R29" s="108"/>
-      <c r="S29" s="108"/>
-      <c r="T29" s="109"/>
+      <c r="K29" s="101"/>
+      <c r="L29" s="102"/>
+      <c r="M29" s="102"/>
+      <c r="N29" s="102"/>
+      <c r="O29" s="102"/>
+      <c r="P29" s="102"/>
+      <c r="Q29" s="102"/>
+      <c r="R29" s="102"/>
+      <c r="S29" s="102"/>
+      <c r="T29" s="103"/>
     </row>
     <row r="30" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
@@ -31087,18 +31102,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1" s="103" t="s">
+      <c r="A1" s="104" t="s">
         <v>765</v>
       </c>
-      <c r="B1" s="103"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="103"/>
-      <c r="E1" s="103"/>
-      <c r="F1" s="103"/>
-      <c r="G1" s="103"/>
-      <c r="H1" s="103"/>
-      <c r="I1" s="103"/>
-      <c r="J1" s="103"/>
+      <c r="B1" s="104"/>
+      <c r="C1" s="104"/>
+      <c r="D1" s="104"/>
+      <c r="E1" s="104"/>
+      <c r="F1" s="104"/>
+      <c r="G1" s="104"/>
+      <c r="H1" s="104"/>
+      <c r="I1" s="104"/>
+      <c r="J1" s="104"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -31109,10 +31124,10 @@
       <c r="A3" s="10" t="s">
         <v>945</v>
       </c>
-      <c r="B3" s="105" t="s">
+      <c r="B3" s="99" t="s">
         <v>486</v>
       </c>
-      <c r="C3" s="106"/>
+      <c r="C3" s="100"/>
       <c r="D3" s="2" t="s">
         <v>82</v>
       </c>
@@ -31168,16 +31183,16 @@
       <c r="H4" s="53"/>
       <c r="I4" s="53"/>
       <c r="J4" s="74"/>
-      <c r="K4" s="107"/>
-      <c r="L4" s="108"/>
-      <c r="M4" s="108"/>
-      <c r="N4" s="108"/>
-      <c r="O4" s="108"/>
-      <c r="P4" s="108"/>
-      <c r="Q4" s="108"/>
-      <c r="R4" s="108"/>
-      <c r="S4" s="108"/>
-      <c r="T4" s="109"/>
+      <c r="K4" s="101"/>
+      <c r="L4" s="102"/>
+      <c r="M4" s="102"/>
+      <c r="N4" s="102"/>
+      <c r="O4" s="102"/>
+      <c r="P4" s="102"/>
+      <c r="Q4" s="102"/>
+      <c r="R4" s="102"/>
+      <c r="S4" s="102"/>
+      <c r="T4" s="103"/>
     </row>
     <row r="5" spans="1:20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="37" t="str">
@@ -32411,16 +32426,16 @@
       <c r="H30" s="53"/>
       <c r="I30" s="53"/>
       <c r="J30" s="53"/>
-      <c r="K30" s="107"/>
-      <c r="L30" s="108"/>
-      <c r="M30" s="108"/>
-      <c r="N30" s="108"/>
-      <c r="O30" s="108"/>
-      <c r="P30" s="108"/>
-      <c r="Q30" s="108"/>
-      <c r="R30" s="108"/>
-      <c r="S30" s="108"/>
-      <c r="T30" s="109"/>
+      <c r="K30" s="101"/>
+      <c r="L30" s="102"/>
+      <c r="M30" s="102"/>
+      <c r="N30" s="102"/>
+      <c r="O30" s="102"/>
+      <c r="P30" s="102"/>
+      <c r="Q30" s="102"/>
+      <c r="R30" s="102"/>
+      <c r="S30" s="102"/>
+      <c r="T30" s="103"/>
     </row>
     <row r="31" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="15" t="s">
@@ -37666,18 +37681,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1" s="103" t="s">
+      <c r="A1" s="104" t="s">
         <v>765</v>
       </c>
-      <c r="B1" s="103"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="103"/>
-      <c r="E1" s="103"/>
-      <c r="F1" s="103"/>
-      <c r="G1" s="103"/>
-      <c r="H1" s="103"/>
-      <c r="I1" s="103"/>
-      <c r="J1" s="103"/>
+      <c r="B1" s="104"/>
+      <c r="C1" s="104"/>
+      <c r="D1" s="104"/>
+      <c r="E1" s="104"/>
+      <c r="F1" s="104"/>
+      <c r="G1" s="104"/>
+      <c r="H1" s="104"/>
+      <c r="I1" s="104"/>
+      <c r="J1" s="104"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -37690,10 +37705,10 @@
       <c r="A3" s="10" t="s">
         <v>972</v>
       </c>
-      <c r="B3" s="105" t="s">
+      <c r="B3" s="99" t="s">
         <v>486</v>
       </c>
-      <c r="C3" s="106"/>
+      <c r="C3" s="100"/>
       <c r="D3" s="2" t="s">
         <v>82</v>
       </c>
@@ -37749,16 +37764,16 @@
       <c r="H4" s="53"/>
       <c r="I4" s="53"/>
       <c r="J4" s="74"/>
-      <c r="K4" s="107"/>
-      <c r="L4" s="108"/>
-      <c r="M4" s="108"/>
-      <c r="N4" s="108"/>
-      <c r="O4" s="108"/>
-      <c r="P4" s="108"/>
-      <c r="Q4" s="108"/>
-      <c r="R4" s="108"/>
-      <c r="S4" s="108"/>
-      <c r="T4" s="109"/>
+      <c r="K4" s="101"/>
+      <c r="L4" s="102"/>
+      <c r="M4" s="102"/>
+      <c r="N4" s="102"/>
+      <c r="O4" s="102"/>
+      <c r="P4" s="102"/>
+      <c r="Q4" s="102"/>
+      <c r="R4" s="102"/>
+      <c r="S4" s="102"/>
+      <c r="T4" s="103"/>
     </row>
     <row r="5" spans="1:20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="37" t="str">
@@ -38938,16 +38953,16 @@
       <c r="H29" s="53"/>
       <c r="I29" s="53"/>
       <c r="J29" s="53"/>
-      <c r="K29" s="107"/>
-      <c r="L29" s="108"/>
-      <c r="M29" s="108"/>
-      <c r="N29" s="108"/>
-      <c r="O29" s="108"/>
-      <c r="P29" s="108"/>
-      <c r="Q29" s="108"/>
-      <c r="R29" s="108"/>
-      <c r="S29" s="108"/>
-      <c r="T29" s="109"/>
+      <c r="K29" s="101"/>
+      <c r="L29" s="102"/>
+      <c r="M29" s="102"/>
+      <c r="N29" s="102"/>
+      <c r="O29" s="102"/>
+      <c r="P29" s="102"/>
+      <c r="Q29" s="102"/>
+      <c r="R29" s="102"/>
+      <c r="S29" s="102"/>
+      <c r="T29" s="103"/>
     </row>
     <row r="30" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="44" t="s">
@@ -40274,18 +40289,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1" s="103" t="s">
+      <c r="A1" s="104" t="s">
         <v>765</v>
       </c>
-      <c r="B1" s="103"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="103"/>
-      <c r="E1" s="103"/>
-      <c r="F1" s="103"/>
-      <c r="G1" s="103"/>
-      <c r="H1" s="103"/>
-      <c r="I1" s="103"/>
-      <c r="J1" s="103"/>
+      <c r="B1" s="104"/>
+      <c r="C1" s="104"/>
+      <c r="D1" s="104"/>
+      <c r="E1" s="104"/>
+      <c r="F1" s="104"/>
+      <c r="G1" s="104"/>
+      <c r="H1" s="104"/>
+      <c r="I1" s="104"/>
+      <c r="J1" s="104"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -40298,10 +40313,10 @@
       <c r="A3" s="10" t="s">
         <v>972</v>
       </c>
-      <c r="B3" s="105" t="s">
+      <c r="B3" s="99" t="s">
         <v>486</v>
       </c>
-      <c r="C3" s="106"/>
+      <c r="C3" s="100"/>
       <c r="D3" s="2" t="s">
         <v>82</v>
       </c>
@@ -40357,16 +40372,16 @@
       <c r="H4" s="53"/>
       <c r="I4" s="53"/>
       <c r="J4" s="74"/>
-      <c r="K4" s="107"/>
-      <c r="L4" s="108"/>
-      <c r="M4" s="108"/>
-      <c r="N4" s="108"/>
-      <c r="O4" s="108"/>
-      <c r="P4" s="108"/>
-      <c r="Q4" s="108"/>
-      <c r="R4" s="108"/>
-      <c r="S4" s="108"/>
-      <c r="T4" s="109"/>
+      <c r="K4" s="101"/>
+      <c r="L4" s="102"/>
+      <c r="M4" s="102"/>
+      <c r="N4" s="102"/>
+      <c r="O4" s="102"/>
+      <c r="P4" s="102"/>
+      <c r="Q4" s="102"/>
+      <c r="R4" s="102"/>
+      <c r="S4" s="102"/>
+      <c r="T4" s="103"/>
     </row>
     <row r="5" spans="1:20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="37" t="str">
@@ -41546,16 +41561,16 @@
       <c r="H29" s="53"/>
       <c r="I29" s="53"/>
       <c r="J29" s="53"/>
-      <c r="K29" s="107"/>
-      <c r="L29" s="108"/>
-      <c r="M29" s="108"/>
-      <c r="N29" s="108"/>
-      <c r="O29" s="108"/>
-      <c r="P29" s="108"/>
-      <c r="Q29" s="108"/>
-      <c r="R29" s="108"/>
-      <c r="S29" s="108"/>
-      <c r="T29" s="109"/>
+      <c r="K29" s="101"/>
+      <c r="L29" s="102"/>
+      <c r="M29" s="102"/>
+      <c r="N29" s="102"/>
+      <c r="O29" s="102"/>
+      <c r="P29" s="102"/>
+      <c r="Q29" s="102"/>
+      <c r="R29" s="102"/>
+      <c r="S29" s="102"/>
+      <c r="T29" s="103"/>
     </row>
     <row r="30" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A30" s="44" t="s">
@@ -43591,7 +43606,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="3" t="str">
-        <f t="shared" ref="G3:G54" si="0">IF(OR(D4="",E4="",F4=""),"",CONCATENATE("0x",DEC2HEX(MOD(F4,64)+E4*POWER(2,6)+D4*POWER(2,16),8)))</f>
+        <f t="shared" ref="G4:G54" si="0">IF(OR(D4="",E4="",F4=""),"",CONCATENATE("0x",DEC2HEX(MOD(F4,64)+E4*POWER(2,6)+D4*POWER(2,16),8)))</f>
         <v>0x00010081</v>
       </c>
       <c r="H4" s="3"/>
@@ -44578,17 +44593,17 @@
       </c>
     </row>
     <row r="2" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A2" s="100" t="s">
+      <c r="A2" s="106" t="s">
         <v>88</v>
       </c>
-      <c r="B2" s="100"/>
-      <c r="C2" s="100"/>
-      <c r="D2" s="100"/>
-      <c r="E2" s="100"/>
-      <c r="F2" s="100"/>
-      <c r="G2" s="100"/>
-      <c r="H2" s="100"/>
-      <c r="I2" s="100"/>
+      <c r="B2" s="106"/>
+      <c r="C2" s="106"/>
+      <c r="D2" s="106"/>
+      <c r="E2" s="106"/>
+      <c r="F2" s="106"/>
+      <c r="G2" s="106"/>
+      <c r="H2" s="106"/>
+      <c r="I2" s="106"/>
       <c r="J2" s="3" t="s">
         <v>89</v>
       </c>
@@ -44930,7 +44945,7 @@
       <c r="L12" s="18" t="s">
         <v>344</v>
       </c>
-      <c r="M12" s="101" t="s">
+      <c r="M12" s="107" t="s">
         <v>481</v>
       </c>
       <c r="R12" s="17" t="s">
@@ -44960,7 +44975,7 @@
       <c r="L13" s="18" t="s">
         <v>344</v>
       </c>
-      <c r="M13" s="101"/>
+      <c r="M13" s="107"/>
       <c r="R13" s="17" t="s">
         <v>116</v>
       </c>
@@ -44988,7 +45003,7 @@
       <c r="L14" s="18" t="s">
         <v>343</v>
       </c>
-      <c r="M14" s="101"/>
+      <c r="M14" s="107"/>
       <c r="R14" s="17" t="s">
         <v>116</v>
       </c>
@@ -45016,7 +45031,7 @@
       <c r="L15" s="18" t="s">
         <v>343</v>
       </c>
-      <c r="M15" s="101"/>
+      <c r="M15" s="107"/>
       <c r="R15" s="17" t="s">
         <v>116</v>
       </c>
@@ -45044,7 +45059,7 @@
       <c r="L16" s="18" t="s">
         <v>343</v>
       </c>
-      <c r="M16" s="101"/>
+      <c r="M16" s="107"/>
       <c r="R16" s="17" t="s">
         <v>116</v>
       </c>
@@ -45072,7 +45087,7 @@
       <c r="L17" s="18" t="s">
         <v>343</v>
       </c>
-      <c r="M17" s="101"/>
+      <c r="M17" s="107"/>
       <c r="R17" s="17" t="s">
         <v>116</v>
       </c>
@@ -45100,7 +45115,7 @@
       <c r="L18" s="18" t="s">
         <v>343</v>
       </c>
-      <c r="M18" s="101"/>
+      <c r="M18" s="107"/>
       <c r="R18" s="17" t="s">
         <v>116</v>
       </c>
@@ -45126,7 +45141,7 @@
       <c r="L19" s="18" t="s">
         <v>343</v>
       </c>
-      <c r="M19" s="101"/>
+      <c r="M19" s="107"/>
       <c r="R19" s="17" t="s">
         <v>116</v>
       </c>
@@ -45152,7 +45167,7 @@
       <c r="L20" s="18" t="s">
         <v>343</v>
       </c>
-      <c r="M20" s="101"/>
+      <c r="M20" s="107"/>
       <c r="R20" s="17" t="s">
         <v>116</v>
       </c>
@@ -45180,7 +45195,7 @@
       <c r="L21" s="18" t="s">
         <v>343</v>
       </c>
-      <c r="M21" s="101"/>
+      <c r="M21" s="107"/>
       <c r="R21" s="17" t="s">
         <v>116</v>
       </c>
@@ -45208,7 +45223,7 @@
       <c r="L22" s="18" t="s">
         <v>343</v>
       </c>
-      <c r="M22" s="101"/>
+      <c r="M22" s="107"/>
       <c r="S22" s="1"/>
       <c r="T22" s="1"/>
       <c r="U22" s="1"/>
@@ -45237,7 +45252,7 @@
       <c r="L23" s="18" t="s">
         <v>343</v>
       </c>
-      <c r="M23" s="101"/>
+      <c r="M23" s="107"/>
       <c r="R23" s="17" t="s">
         <v>116</v>
       </c>
@@ -45271,7 +45286,7 @@
       <c r="L24" s="8" t="s">
         <v>1013</v>
       </c>
-      <c r="M24" s="102" t="s">
+      <c r="M24" s="108" t="s">
         <v>482</v>
       </c>
     </row>
@@ -45297,7 +45312,7 @@
       <c r="L25" s="8" t="s">
         <v>1012</v>
       </c>
-      <c r="M25" s="102"/>
+      <c r="M25" s="108"/>
     </row>
     <row r="26" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26" s="15" t="s">
@@ -45362,18 +45377,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="103" t="s">
+      <c r="A1" s="104" t="s">
         <v>765</v>
       </c>
-      <c r="B1" s="103"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="103"/>
-      <c r="E1" s="103"/>
-      <c r="F1" s="103"/>
-      <c r="G1" s="103"/>
-      <c r="H1" s="103"/>
-      <c r="I1" s="103"/>
-      <c r="J1" s="103"/>
+      <c r="B1" s="104"/>
+      <c r="C1" s="104"/>
+      <c r="D1" s="104"/>
+      <c r="E1" s="104"/>
+      <c r="F1" s="104"/>
+      <c r="G1" s="104"/>
+      <c r="H1" s="104"/>
+      <c r="I1" s="104"/>
+      <c r="J1" s="104"/>
       <c r="K1" s="3"/>
     </row>
     <row r="2" spans="1:22" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -45427,30 +45442,30 @@
       </c>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" s="100" t="s">
+      <c r="A4" s="106" t="s">
         <v>135</v>
       </c>
-      <c r="B4" s="100"/>
-      <c r="C4" s="100"/>
-      <c r="D4" s="100"/>
-      <c r="E4" s="100"/>
-      <c r="F4" s="100"/>
-      <c r="G4" s="100"/>
-      <c r="H4" s="100"/>
-      <c r="I4" s="100"/>
-      <c r="J4" s="100"/>
-      <c r="K4" s="100"/>
-      <c r="L4" s="100"/>
-      <c r="M4" s="100"/>
-      <c r="N4" s="100"/>
-      <c r="O4" s="100"/>
-      <c r="P4" s="100"/>
-      <c r="Q4" s="100"/>
-      <c r="R4" s="100"/>
-      <c r="S4" s="100"/>
-      <c r="T4" s="100"/>
-      <c r="U4" s="100"/>
-      <c r="V4" s="100"/>
+      <c r="B4" s="106"/>
+      <c r="C4" s="106"/>
+      <c r="D4" s="106"/>
+      <c r="E4" s="106"/>
+      <c r="F4" s="106"/>
+      <c r="G4" s="106"/>
+      <c r="H4" s="106"/>
+      <c r="I4" s="106"/>
+      <c r="J4" s="106"/>
+      <c r="K4" s="106"/>
+      <c r="L4" s="106"/>
+      <c r="M4" s="106"/>
+      <c r="N4" s="106"/>
+      <c r="O4" s="106"/>
+      <c r="P4" s="106"/>
+      <c r="Q4" s="106"/>
+      <c r="R4" s="106"/>
+      <c r="S4" s="106"/>
+      <c r="T4" s="106"/>
+      <c r="U4" s="106"/>
+      <c r="V4" s="106"/>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A5" s="37" t="str">
@@ -46372,30 +46387,30 @@
       <c r="J29" s="3"/>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A30" s="100" t="s">
+      <c r="A30" s="106" t="s">
         <v>138</v>
       </c>
-      <c r="B30" s="100"/>
-      <c r="C30" s="100"/>
-      <c r="D30" s="100"/>
-      <c r="E30" s="100"/>
-      <c r="F30" s="100"/>
-      <c r="G30" s="100"/>
-      <c r="H30" s="100"/>
-      <c r="I30" s="100"/>
-      <c r="J30" s="100"/>
-      <c r="K30" s="100"/>
-      <c r="L30" s="100"/>
-      <c r="M30" s="100"/>
-      <c r="N30" s="100"/>
-      <c r="O30" s="100"/>
-      <c r="P30" s="100"/>
-      <c r="Q30" s="100"/>
-      <c r="R30" s="100"/>
-      <c r="S30" s="100"/>
-      <c r="T30" s="100"/>
-      <c r="U30" s="100"/>
-      <c r="V30" s="100"/>
+      <c r="B30" s="106"/>
+      <c r="C30" s="106"/>
+      <c r="D30" s="106"/>
+      <c r="E30" s="106"/>
+      <c r="F30" s="106"/>
+      <c r="G30" s="106"/>
+      <c r="H30" s="106"/>
+      <c r="I30" s="106"/>
+      <c r="J30" s="106"/>
+      <c r="K30" s="106"/>
+      <c r="L30" s="106"/>
+      <c r="M30" s="106"/>
+      <c r="N30" s="106"/>
+      <c r="O30" s="106"/>
+      <c r="P30" s="106"/>
+      <c r="Q30" s="106"/>
+      <c r="R30" s="106"/>
+      <c r="S30" s="106"/>
+      <c r="T30" s="106"/>
+      <c r="U30" s="106"/>
+      <c r="V30" s="106"/>
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
@@ -46655,15 +46670,15 @@
         <v>93</v>
       </c>
       <c r="J39" s="3"/>
-      <c r="O39" s="104" t="s">
+      <c r="O39" s="109" t="s">
         <v>154</v>
       </c>
-      <c r="P39" s="104"/>
-      <c r="Q39" s="104"/>
-      <c r="R39" s="104"/>
-      <c r="S39" s="104"/>
-      <c r="T39" s="104"/>
-      <c r="U39" s="104"/>
+      <c r="P39" s="109"/>
+      <c r="Q39" s="109"/>
+      <c r="R39" s="109"/>
+      <c r="S39" s="109"/>
+      <c r="T39" s="109"/>
+      <c r="U39" s="109"/>
     </row>
     <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="15" t="s">
@@ -46700,13 +46715,13 @@
       <c r="N40" s="17" t="s">
         <v>352</v>
       </c>
-      <c r="O40" s="104"/>
-      <c r="P40" s="104"/>
-      <c r="Q40" s="104"/>
-      <c r="R40" s="104"/>
-      <c r="S40" s="104"/>
-      <c r="T40" s="104"/>
-      <c r="U40" s="104"/>
+      <c r="O40" s="109"/>
+      <c r="P40" s="109"/>
+      <c r="Q40" s="109"/>
+      <c r="R40" s="109"/>
+      <c r="S40" s="109"/>
+      <c r="T40" s="109"/>
+      <c r="U40" s="109"/>
     </row>
     <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="15" t="s">
@@ -46730,13 +46745,13 @@
         <v>93</v>
       </c>
       <c r="J41" s="3"/>
-      <c r="O41" s="104"/>
-      <c r="P41" s="104"/>
-      <c r="Q41" s="104"/>
-      <c r="R41" s="104"/>
-      <c r="S41" s="104"/>
-      <c r="T41" s="104"/>
-      <c r="U41" s="104"/>
+      <c r="O41" s="109"/>
+      <c r="P41" s="109"/>
+      <c r="Q41" s="109"/>
+      <c r="R41" s="109"/>
+      <c r="S41" s="109"/>
+      <c r="T41" s="109"/>
+      <c r="U41" s="109"/>
     </row>
     <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="15" t="s">
@@ -46772,13 +46787,13 @@
       <c r="N42" s="17" t="s">
         <v>352</v>
       </c>
-      <c r="O42" s="104"/>
-      <c r="P42" s="104"/>
-      <c r="Q42" s="104"/>
-      <c r="R42" s="104"/>
-      <c r="S42" s="104"/>
-      <c r="T42" s="104"/>
-      <c r="U42" s="104"/>
+      <c r="O42" s="109"/>
+      <c r="P42" s="109"/>
+      <c r="Q42" s="109"/>
+      <c r="R42" s="109"/>
+      <c r="S42" s="109"/>
+      <c r="T42" s="109"/>
+      <c r="U42" s="109"/>
     </row>
     <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="15" t="s">
@@ -46814,13 +46829,13 @@
       <c r="N43" s="17" t="s">
         <v>352</v>
       </c>
-      <c r="O43" s="104"/>
-      <c r="P43" s="104"/>
-      <c r="Q43" s="104"/>
-      <c r="R43" s="104"/>
-      <c r="S43" s="104"/>
-      <c r="T43" s="104"/>
-      <c r="U43" s="104"/>
+      <c r="O43" s="109"/>
+      <c r="P43" s="109"/>
+      <c r="Q43" s="109"/>
+      <c r="R43" s="109"/>
+      <c r="S43" s="109"/>
+      <c r="T43" s="109"/>
+      <c r="U43" s="109"/>
     </row>
     <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="15" t="s">
@@ -46843,13 +46858,13 @@
         <v>93</v>
       </c>
       <c r="J44" s="3"/>
-      <c r="O44" s="104"/>
-      <c r="P44" s="104"/>
-      <c r="Q44" s="104"/>
-      <c r="R44" s="104"/>
-      <c r="S44" s="104"/>
-      <c r="T44" s="104"/>
-      <c r="U44" s="104"/>
+      <c r="O44" s="109"/>
+      <c r="P44" s="109"/>
+      <c r="Q44" s="109"/>
+      <c r="R44" s="109"/>
+      <c r="S44" s="109"/>
+      <c r="T44" s="109"/>
+      <c r="U44" s="109"/>
     </row>
     <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="15" t="s">
@@ -46884,13 +46899,13 @@
       <c r="N45" s="17" t="s">
         <v>352</v>
       </c>
-      <c r="O45" s="104"/>
-      <c r="P45" s="104"/>
-      <c r="Q45" s="104"/>
-      <c r="R45" s="104"/>
-      <c r="S45" s="104"/>
-      <c r="T45" s="104"/>
-      <c r="U45" s="104"/>
+      <c r="O45" s="109"/>
+      <c r="P45" s="109"/>
+      <c r="Q45" s="109"/>
+      <c r="R45" s="109"/>
+      <c r="S45" s="109"/>
+      <c r="T45" s="109"/>
+      <c r="U45" s="109"/>
     </row>
     <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="15" t="s">
@@ -46913,13 +46928,13 @@
         <v>93</v>
       </c>
       <c r="J46" s="3"/>
-      <c r="O46" s="104"/>
-      <c r="P46" s="104"/>
-      <c r="Q46" s="104"/>
-      <c r="R46" s="104"/>
-      <c r="S46" s="104"/>
-      <c r="T46" s="104"/>
-      <c r="U46" s="104"/>
+      <c r="O46" s="109"/>
+      <c r="P46" s="109"/>
+      <c r="Q46" s="109"/>
+      <c r="R46" s="109"/>
+      <c r="S46" s="109"/>
+      <c r="T46" s="109"/>
+      <c r="U46" s="109"/>
     </row>
     <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="15" t="s">
@@ -46954,13 +46969,13 @@
       <c r="N47" s="17" t="s">
         <v>352</v>
       </c>
-      <c r="O47" s="104"/>
-      <c r="P47" s="104"/>
-      <c r="Q47" s="104"/>
-      <c r="R47" s="104"/>
-      <c r="S47" s="104"/>
-      <c r="T47" s="104"/>
-      <c r="U47" s="104"/>
+      <c r="O47" s="109"/>
+      <c r="P47" s="109"/>
+      <c r="Q47" s="109"/>
+      <c r="R47" s="109"/>
+      <c r="S47" s="109"/>
+      <c r="T47" s="109"/>
+      <c r="U47" s="109"/>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="15" t="s">
@@ -46996,13 +47011,13 @@
       <c r="N48" s="17" t="s">
         <v>352</v>
       </c>
-      <c r="O48" s="104"/>
-      <c r="P48" s="104"/>
-      <c r="Q48" s="104"/>
-      <c r="R48" s="104"/>
-      <c r="S48" s="104"/>
-      <c r="T48" s="104"/>
-      <c r="U48" s="104"/>
+      <c r="O48" s="109"/>
+      <c r="P48" s="109"/>
+      <c r="Q48" s="109"/>
+      <c r="R48" s="109"/>
+      <c r="S48" s="109"/>
+      <c r="T48" s="109"/>
+      <c r="U48" s="109"/>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A49" s="15" t="s">
@@ -47026,13 +47041,13 @@
         <v>93</v>
       </c>
       <c r="J49" s="3"/>
-      <c r="O49" s="104"/>
-      <c r="P49" s="104"/>
-      <c r="Q49" s="104"/>
-      <c r="R49" s="104"/>
-      <c r="S49" s="104"/>
-      <c r="T49" s="104"/>
-      <c r="U49" s="104"/>
+      <c r="O49" s="109"/>
+      <c r="P49" s="109"/>
+      <c r="Q49" s="109"/>
+      <c r="R49" s="109"/>
+      <c r="S49" s="109"/>
+      <c r="T49" s="109"/>
+      <c r="U49" s="109"/>
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A50" s="15" t="s">
@@ -47183,30 +47198,30 @@
       </c>
     </row>
     <row r="55" spans="1:22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="100" t="s">
+      <c r="A55" s="106" t="s">
         <v>135</v>
       </c>
-      <c r="B55" s="100"/>
-      <c r="C55" s="100"/>
-      <c r="D55" s="100"/>
-      <c r="E55" s="100"/>
-      <c r="F55" s="100"/>
-      <c r="G55" s="100"/>
-      <c r="H55" s="100"/>
-      <c r="I55" s="100"/>
-      <c r="J55" s="100"/>
-      <c r="K55" s="100"/>
-      <c r="L55" s="100"/>
-      <c r="M55" s="100"/>
-      <c r="N55" s="100"/>
-      <c r="O55" s="100"/>
-      <c r="P55" s="100"/>
-      <c r="Q55" s="100"/>
-      <c r="R55" s="100"/>
-      <c r="S55" s="100"/>
-      <c r="T55" s="100"/>
-      <c r="U55" s="100"/>
-      <c r="V55" s="100"/>
+      <c r="B55" s="106"/>
+      <c r="C55" s="106"/>
+      <c r="D55" s="106"/>
+      <c r="E55" s="106"/>
+      <c r="F55" s="106"/>
+      <c r="G55" s="106"/>
+      <c r="H55" s="106"/>
+      <c r="I55" s="106"/>
+      <c r="J55" s="106"/>
+      <c r="K55" s="106"/>
+      <c r="L55" s="106"/>
+      <c r="M55" s="106"/>
+      <c r="N55" s="106"/>
+      <c r="O55" s="106"/>
+      <c r="P55" s="106"/>
+      <c r="Q55" s="106"/>
+      <c r="R55" s="106"/>
+      <c r="S55" s="106"/>
+      <c r="T55" s="106"/>
+      <c r="U55" s="106"/>
+      <c r="V55" s="106"/>
     </row>
     <row r="56" spans="1:22" ht="60" x14ac:dyDescent="0.25">
       <c r="A56" s="15" t="s">
@@ -48140,18 +48155,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1" s="103" t="s">
+      <c r="A1" s="104" t="s">
         <v>765</v>
       </c>
-      <c r="B1" s="103"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="103"/>
-      <c r="E1" s="103"/>
-      <c r="F1" s="103"/>
-      <c r="G1" s="103"/>
-      <c r="H1" s="103"/>
-      <c r="I1" s="103"/>
-      <c r="J1" s="103"/>
+      <c r="B1" s="104"/>
+      <c r="C1" s="104"/>
+      <c r="D1" s="104"/>
+      <c r="E1" s="104"/>
+      <c r="F1" s="104"/>
+      <c r="G1" s="104"/>
+      <c r="H1" s="104"/>
+      <c r="I1" s="104"/>
+      <c r="J1" s="104"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -48162,10 +48177,10 @@
       <c r="A3" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="B3" s="105" t="s">
+      <c r="B3" s="99" t="s">
         <v>486</v>
       </c>
-      <c r="C3" s="106"/>
+      <c r="C3" s="100"/>
       <c r="D3" s="2" t="s">
         <v>82</v>
       </c>
@@ -48221,16 +48236,16 @@
       <c r="H4" s="53"/>
       <c r="I4" s="53"/>
       <c r="J4" s="74"/>
-      <c r="K4" s="107"/>
-      <c r="L4" s="108"/>
-      <c r="M4" s="108"/>
-      <c r="N4" s="108"/>
-      <c r="O4" s="108"/>
-      <c r="P4" s="108"/>
-      <c r="Q4" s="108"/>
-      <c r="R4" s="108"/>
-      <c r="S4" s="108"/>
-      <c r="T4" s="109"/>
+      <c r="K4" s="101"/>
+      <c r="L4" s="102"/>
+      <c r="M4" s="102"/>
+      <c r="N4" s="102"/>
+      <c r="O4" s="102"/>
+      <c r="P4" s="102"/>
+      <c r="Q4" s="102"/>
+      <c r="R4" s="102"/>
+      <c r="S4" s="102"/>
+      <c r="T4" s="103"/>
     </row>
     <row r="5" spans="1:20" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="37" t="str">
@@ -49464,16 +49479,16 @@
       <c r="H30" s="53"/>
       <c r="I30" s="53"/>
       <c r="J30" s="53"/>
-      <c r="K30" s="107"/>
-      <c r="L30" s="108"/>
-      <c r="M30" s="108"/>
-      <c r="N30" s="108"/>
-      <c r="O30" s="108"/>
-      <c r="P30" s="108"/>
-      <c r="Q30" s="108"/>
-      <c r="R30" s="108"/>
-      <c r="S30" s="108"/>
-      <c r="T30" s="109"/>
+      <c r="K30" s="101"/>
+      <c r="L30" s="102"/>
+      <c r="M30" s="102"/>
+      <c r="N30" s="102"/>
+      <c r="O30" s="102"/>
+      <c r="P30" s="102"/>
+      <c r="Q30" s="102"/>
+      <c r="R30" s="102"/>
+      <c r="S30" s="102"/>
+      <c r="T30" s="103"/>
     </row>
     <row r="31" spans="1:20" ht="30" x14ac:dyDescent="0.25">
       <c r="A31" s="15" t="s">
@@ -54733,21 +54748,25 @@
     <col min="13" max="13" width="12.5703125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="14.28515625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="15.140625" customWidth="1"/>
+    <col min="17" max="17" width="16" customWidth="1"/>
+    <col min="18" max="18" width="16.5703125" customWidth="1"/>
+    <col min="19" max="19" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="103" t="s">
+      <c r="A1" s="104" t="s">
         <v>765</v>
       </c>
-      <c r="B1" s="103"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="103"/>
-      <c r="E1" s="103"/>
-      <c r="F1" s="103"/>
-      <c r="G1" s="103"/>
-      <c r="H1" s="103"/>
-      <c r="I1" s="103"/>
-      <c r="J1" s="103"/>
+      <c r="B1" s="104"/>
+      <c r="C1" s="104"/>
+      <c r="D1" s="104"/>
+      <c r="E1" s="104"/>
+      <c r="F1" s="104"/>
+      <c r="G1" s="104"/>
+      <c r="H1" s="104"/>
+      <c r="I1" s="104"/>
+      <c r="J1" s="104"/>
       <c r="K1" s="3"/>
     </row>
     <row r="2" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -54790,15 +54809,33 @@
       <c r="M2" s="1" t="s">
         <v>1001</v>
       </c>
+      <c r="N2" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>1034</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>1035</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>1036</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>772</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>1033</v>
+      </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
         <v>603</v>
       </c>
-      <c r="B3" s="105" t="s">
+      <c r="B3" s="99" t="s">
         <v>486</v>
       </c>
-      <c r="C3" s="106"/>
+      <c r="C3" s="100"/>
       <c r="D3" s="2" t="s">
         <v>82</v>
       </c>
@@ -54849,16 +54886,16 @@
       <c r="H4" s="55"/>
       <c r="I4" s="55"/>
       <c r="J4" s="56"/>
-      <c r="K4" s="107"/>
-      <c r="L4" s="108"/>
-      <c r="M4" s="108"/>
-      <c r="N4" s="108"/>
-      <c r="O4" s="108"/>
-      <c r="P4" s="108"/>
-      <c r="Q4" s="108"/>
-      <c r="R4" s="108"/>
-      <c r="S4" s="108"/>
-      <c r="T4" s="109"/>
+      <c r="K4" s="101"/>
+      <c r="L4" s="102"/>
+      <c r="M4" s="102"/>
+      <c r="N4" s="102"/>
+      <c r="O4" s="102"/>
+      <c r="P4" s="102"/>
+      <c r="Q4" s="102"/>
+      <c r="R4" s="102"/>
+      <c r="S4" s="102"/>
+      <c r="T4" s="103"/>
     </row>
     <row r="5" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="37" t="str">
@@ -54938,16 +54975,16 @@
         <v>R</v>
       </c>
       <c r="J6" s="3"/>
-      <c r="K6" s="107"/>
-      <c r="L6" s="108"/>
-      <c r="M6" s="108"/>
-      <c r="N6" s="108"/>
-      <c r="O6" s="108"/>
-      <c r="P6" s="108"/>
-      <c r="Q6" s="108"/>
-      <c r="R6" s="108"/>
-      <c r="S6" s="108"/>
-      <c r="T6" s="109"/>
+      <c r="K6" s="101"/>
+      <c r="L6" s="102"/>
+      <c r="M6" s="102"/>
+      <c r="N6" s="102"/>
+      <c r="O6" s="102"/>
+      <c r="P6" s="102"/>
+      <c r="Q6" s="102"/>
+      <c r="R6" s="102"/>
+      <c r="S6" s="102"/>
+      <c r="T6" s="103"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="54" t="str">
@@ -55782,16 +55819,16 @@
       <c r="H29" s="53"/>
       <c r="I29" s="53"/>
       <c r="J29" s="53"/>
-      <c r="K29" s="107"/>
-      <c r="L29" s="108"/>
-      <c r="M29" s="108"/>
-      <c r="N29" s="108"/>
-      <c r="O29" s="108"/>
-      <c r="P29" s="108"/>
-      <c r="Q29" s="108"/>
-      <c r="R29" s="108"/>
-      <c r="S29" s="108"/>
-      <c r="T29" s="109"/>
+      <c r="K29" s="101"/>
+      <c r="L29" s="102"/>
+      <c r="M29" s="102"/>
+      <c r="N29" s="102"/>
+      <c r="O29" s="102"/>
+      <c r="P29" s="102"/>
+      <c r="Q29" s="102"/>
+      <c r="R29" s="102"/>
+      <c r="S29" s="102"/>
+      <c r="T29" s="103"/>
     </row>
     <row r="30" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A30" s="15" t="s">
@@ -55997,18 +56034,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1" s="103" t="s">
+      <c r="A1" s="104" t="s">
         <v>765</v>
       </c>
-      <c r="B1" s="103"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="103"/>
-      <c r="E1" s="103"/>
-      <c r="F1" s="103"/>
-      <c r="G1" s="103"/>
-      <c r="H1" s="103"/>
-      <c r="I1" s="103"/>
-      <c r="J1" s="103"/>
+      <c r="B1" s="104"/>
+      <c r="C1" s="104"/>
+      <c r="D1" s="104"/>
+      <c r="E1" s="104"/>
+      <c r="F1" s="104"/>
+      <c r="G1" s="104"/>
+      <c r="H1" s="104"/>
+      <c r="I1" s="104"/>
+      <c r="J1" s="104"/>
       <c r="K1" s="3"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
@@ -56075,16 +56112,16 @@
       <c r="H4" s="55"/>
       <c r="I4" s="55"/>
       <c r="J4" s="56"/>
-      <c r="K4" s="107"/>
-      <c r="L4" s="108"/>
-      <c r="M4" s="108"/>
-      <c r="N4" s="108"/>
-      <c r="O4" s="108"/>
-      <c r="P4" s="108"/>
-      <c r="Q4" s="108"/>
-      <c r="R4" s="108"/>
-      <c r="S4" s="108"/>
-      <c r="T4" s="109"/>
+      <c r="K4" s="101"/>
+      <c r="L4" s="102"/>
+      <c r="M4" s="102"/>
+      <c r="N4" s="102"/>
+      <c r="O4" s="102"/>
+      <c r="P4" s="102"/>
+      <c r="Q4" s="102"/>
+      <c r="R4" s="102"/>
+      <c r="S4" s="102"/>
+      <c r="T4" s="103"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="37" t="str">
@@ -58036,18 +58073,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="A1" s="103" t="s">
+      <c r="A1" s="104" t="s">
         <v>765</v>
       </c>
-      <c r="B1" s="103"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="103"/>
-      <c r="E1" s="103"/>
-      <c r="F1" s="103"/>
-      <c r="G1" s="103"/>
-      <c r="H1" s="103"/>
-      <c r="I1" s="103"/>
-      <c r="J1" s="103"/>
+      <c r="B1" s="104"/>
+      <c r="C1" s="104"/>
+      <c r="D1" s="104"/>
+      <c r="E1" s="104"/>
+      <c r="F1" s="104"/>
+      <c r="G1" s="104"/>
+      <c r="H1" s="104"/>
+      <c r="I1" s="104"/>
+      <c r="J1" s="104"/>
       <c r="K1" s="3"/>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
@@ -58116,16 +58153,16 @@
       <c r="H4" s="55"/>
       <c r="I4" s="55"/>
       <c r="J4" s="56"/>
-      <c r="K4" s="107"/>
-      <c r="L4" s="108"/>
-      <c r="M4" s="108"/>
-      <c r="N4" s="108"/>
-      <c r="O4" s="108"/>
-      <c r="P4" s="108"/>
-      <c r="Q4" s="108"/>
-      <c r="R4" s="108"/>
-      <c r="S4" s="108"/>
-      <c r="T4" s="109"/>
+      <c r="K4" s="101"/>
+      <c r="L4" s="102"/>
+      <c r="M4" s="102"/>
+      <c r="N4" s="102"/>
+      <c r="O4" s="102"/>
+      <c r="P4" s="102"/>
+      <c r="Q4" s="102"/>
+      <c r="R4" s="102"/>
+      <c r="S4" s="102"/>
+      <c r="T4" s="103"/>
     </row>
     <row r="5" spans="1:23" s="69" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A5" s="70" t="str">
@@ -60219,18 +60256,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="103" t="s">
+      <c r="A1" s="104" t="s">
         <v>765</v>
       </c>
-      <c r="B1" s="103"/>
-      <c r="C1" s="103"/>
-      <c r="D1" s="103"/>
-      <c r="E1" s="103"/>
-      <c r="F1" s="103"/>
-      <c r="G1" s="103"/>
-      <c r="H1" s="103"/>
-      <c r="I1" s="103"/>
-      <c r="J1" s="103"/>
+      <c r="B1" s="104"/>
+      <c r="C1" s="104"/>
+      <c r="D1" s="104"/>
+      <c r="E1" s="104"/>
+      <c r="F1" s="104"/>
+      <c r="G1" s="104"/>
+      <c r="H1" s="104"/>
+      <c r="I1" s="104"/>
+      <c r="J1" s="104"/>
       <c r="K1" s="3"/>
     </row>
     <row r="2" spans="1:20" s="1" customFormat="1" x14ac:dyDescent="0.25">
@@ -60243,10 +60280,10 @@
       <c r="A3" s="10" t="s">
         <v>306</v>
       </c>
-      <c r="B3" s="105" t="s">
+      <c r="B3" s="99" t="s">
         <v>486</v>
       </c>
-      <c r="C3" s="106"/>
+      <c r="C3" s="100"/>
       <c r="D3" s="2" t="s">
         <v>82</v>
       </c>
@@ -60294,16 +60331,16 @@
       <c r="H4" s="111"/>
       <c r="I4" s="111"/>
       <c r="J4" s="113"/>
-      <c r="K4" s="107"/>
-      <c r="L4" s="108"/>
-      <c r="M4" s="108"/>
-      <c r="N4" s="108"/>
-      <c r="O4" s="108"/>
-      <c r="P4" s="108"/>
-      <c r="Q4" s="108"/>
-      <c r="R4" s="108"/>
-      <c r="S4" s="108"/>
-      <c r="T4" s="109"/>
+      <c r="K4" s="101"/>
+      <c r="L4" s="102"/>
+      <c r="M4" s="102"/>
+      <c r="N4" s="102"/>
+      <c r="O4" s="102"/>
+      <c r="P4" s="102"/>
+      <c r="Q4" s="102"/>
+      <c r="R4" s="102"/>
+      <c r="S4" s="102"/>
+      <c r="T4" s="103"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A5" s="37" t="str">
@@ -61414,28 +61451,28 @@
       <c r="I37" s="3"/>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A38" s="107" t="s">
+      <c r="A38" s="101" t="s">
         <v>485</v>
       </c>
-      <c r="B38" s="108"/>
-      <c r="C38" s="108"/>
-      <c r="D38" s="108"/>
-      <c r="E38" s="108"/>
-      <c r="F38" s="108"/>
-      <c r="G38" s="108"/>
-      <c r="H38" s="108"/>
-      <c r="I38" s="108"/>
-      <c r="J38" s="109"/>
-      <c r="K38" s="107"/>
-      <c r="L38" s="108"/>
-      <c r="M38" s="108"/>
-      <c r="N38" s="108"/>
-      <c r="O38" s="108"/>
-      <c r="P38" s="108"/>
-      <c r="Q38" s="108"/>
-      <c r="R38" s="108"/>
-      <c r="S38" s="108"/>
-      <c r="T38" s="109"/>
+      <c r="B38" s="102"/>
+      <c r="C38" s="102"/>
+      <c r="D38" s="102"/>
+      <c r="E38" s="102"/>
+      <c r="F38" s="102"/>
+      <c r="G38" s="102"/>
+      <c r="H38" s="102"/>
+      <c r="I38" s="102"/>
+      <c r="J38" s="103"/>
+      <c r="K38" s="101"/>
+      <c r="L38" s="102"/>
+      <c r="M38" s="102"/>
+      <c r="N38" s="102"/>
+      <c r="O38" s="102"/>
+      <c r="P38" s="102"/>
+      <c r="Q38" s="102"/>
+      <c r="R38" s="102"/>
+      <c r="S38" s="102"/>
+      <c r="T38" s="103"/>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A39" s="3"/>
